--- a/data/csv_files/demo_data/dartmouth/demo_dartmouth.xlsx
+++ b/data/csv_files/demo_data/dartmouth/demo_dartmouth.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D2993-F6D1-394E-B5BB-71E5B783EC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30260" yWindow="-2680" windowWidth="17820" windowHeight="23360" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
+    <workbookView xWindow="30260" yWindow="-2680" windowWidth="17820" windowHeight="23360"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="380" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -83,8 +83,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -108,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -116,13 +116,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -141,7 +143,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -292,7 +294,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -316,9 +318,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -342,7 +344,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -377,7 +379,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -395,7 +397,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -420,7 +422,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -456,775 +458,781 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C03222-1F27-AC4C-9C40-659F3B91E4D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C03222-1F27-AC4C-9C40-659F3B91E4D1}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="8" max="8" width="16.7109375" customWidth="true"/>
+    <col min="1" max="1" width="3.7109375" customWidth="true"/>
+    <col min="2" max="2" width="4.7109375" customWidth="true"/>
+    <col min="3" max="3" width="5.2109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
+      <c r="B2" s="0">
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
+      <c r="B3" s="0">
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H3" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
+      <c r="B4" s="0">
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="B5" s="0">
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="0">
+        <v>20</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>11</v>
+      <c r="B7" s="0">
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D7" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
+      <c r="B8" s="0">
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
+      <c r="B9" s="0">
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
+      <c r="B10" s="0">
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
+      <c r="B11" s="0">
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>11</v>
+      <c r="B12" s="0">
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>11</v>
+      <c r="B13" s="0">
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>11</v>
+      <c r="B14" s="0">
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>11</v>
+      <c r="B15" s="0">
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>11</v>
+      <c r="B16" s="0">
+        <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>11</v>
+      <c r="B17" s="0">
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D17" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>11</v>
+      <c r="B18" s="0">
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D18" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>11</v>
+      <c r="B19" s="0">
+        <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D19" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>11</v>
+      <c r="B20" s="0">
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D20" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>11</v>
+      <c r="B21" s="0">
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D21" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>11</v>
+      <c r="B22" s="0">
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D22" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>11</v>
+      <c r="B23" s="0">
+        <v>18</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D23" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>11</v>
+      <c r="B24" s="0">
+        <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D24" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>11</v>
+      <c r="B25" s="0">
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>11</v>
+      <c r="B26" s="0">
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="D26" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>11</v>
+      <c r="B27" s="0">
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D27" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>11</v>
+      <c r="B28" s="0">
+        <v>22</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="D28" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H28" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>11</v>
+      <c r="B29" s="0">
+        <v>18</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D29" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
 </worksheet>
 </file>